--- a/artfynd/A 29705-2021 artfynd.xlsx
+++ b/artfynd/A 29705-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 29705-2021 artfynd.xlsx
+++ b/artfynd/A 29705-2021 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>82313222</v>
       </c>
       <c r="B2" t="n">
-        <v>103250</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105606</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>564688.2377761191</v>
+        <v>564688</v>
       </c>
       <c r="R2" t="n">
-        <v>6884166.917009904</v>
+        <v>6884167</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -753,19 +748,9 @@
           <t>1984-06-10</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1984-06-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -804,12 +789,7 @@
         <v>82313250</v>
       </c>
       <c r="B3" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98600</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>564688.2377761191</v>
+        <v>564688</v>
       </c>
       <c r="R3" t="n">
-        <v>6884166.917009904</v>
+        <v>6884167</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -879,19 +859,9 @@
           <t>1984-06-10</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1984-06-10</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -930,12 +900,7 @@
         <v>82313242</v>
       </c>
       <c r="B4" t="n">
-        <v>98008</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100299</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -967,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>564688.2377761191</v>
+        <v>564688</v>
       </c>
       <c r="R4" t="n">
-        <v>6884166.917009904</v>
+        <v>6884167</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -1005,19 +970,9 @@
           <t>1984-06-10</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1984-06-10</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1056,12 +1011,7 @@
         <v>82313263</v>
       </c>
       <c r="B5" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97454</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>564688.2377761191</v>
+        <v>564688</v>
       </c>
       <c r="R5" t="n">
-        <v>6884166.917009904</v>
+        <v>6884167</v>
       </c>
       <c r="S5" t="n">
         <v>100</v>
@@ -1131,19 +1081,9 @@
           <t>1984-06-10</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>1984-06-10</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1182,12 +1122,7 @@
         <v>82313253</v>
       </c>
       <c r="B6" t="n">
-        <v>96237</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98483</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>564688.2377761191</v>
+        <v>564688</v>
       </c>
       <c r="R6" t="n">
-        <v>6884166.917009904</v>
+        <v>6884167</v>
       </c>
       <c r="S6" t="n">
         <v>100</v>
@@ -1257,19 +1192,9 @@
           <t>1984-06-10</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>1984-06-10</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1308,12 +1233,7 @@
         <v>82313251</v>
       </c>
       <c r="B7" t="n">
-        <v>96254</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98499</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1341,10 +1261,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564688.2377761191</v>
+        <v>564688</v>
       </c>
       <c r="R7" t="n">
-        <v>6884166.917009904</v>
+        <v>6884167</v>
       </c>
       <c r="S7" t="n">
         <v>100</v>
@@ -1379,19 +1299,9 @@
           <t>1984-06-10</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>1984-06-10</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1430,12 +1340,7 @@
         <v>82313249</v>
       </c>
       <c r="B8" t="n">
-        <v>96356</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98602</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,10 +1372,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564688.2377761191</v>
+        <v>564688</v>
       </c>
       <c r="R8" t="n">
-        <v>6884166.917009904</v>
+        <v>6884167</v>
       </c>
       <c r="S8" t="n">
         <v>100</v>
@@ -1505,19 +1410,9 @@
           <t>1984-06-10</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>1984-06-10</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 29705-2021 artfynd.xlsx
+++ b/artfynd/A 29705-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>82313222</v>
       </c>
       <c r="B2" t="n">
-        <v>105606</v>
+        <v>105615</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>82313250</v>
       </c>
       <c r="B3" t="n">
-        <v>98600</v>
+        <v>98606</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>82313242</v>
       </c>
       <c r="B4" t="n">
-        <v>100299</v>
+        <v>100305</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>82313263</v>
       </c>
       <c r="B5" t="n">
-        <v>97454</v>
+        <v>97460</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>82313253</v>
       </c>
       <c r="B6" t="n">
-        <v>98483</v>
+        <v>98489</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>82313251</v>
       </c>
       <c r="B7" t="n">
-        <v>98499</v>
+        <v>98505</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>82313249</v>
       </c>
       <c r="B8" t="n">
-        <v>98602</v>
+        <v>98608</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 29705-2021 artfynd.xlsx
+++ b/artfynd/A 29705-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>82313222</v>
       </c>
       <c r="B2" t="n">
-        <v>105615</v>
+        <v>105627</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>82313250</v>
       </c>
       <c r="B3" t="n">
-        <v>98606</v>
+        <v>98609</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>82313242</v>
       </c>
       <c r="B4" t="n">
-        <v>100305</v>
+        <v>100309</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>82313263</v>
       </c>
       <c r="B5" t="n">
-        <v>97460</v>
+        <v>97462</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>82313253</v>
       </c>
       <c r="B6" t="n">
-        <v>98489</v>
+        <v>98492</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>82313251</v>
       </c>
       <c r="B7" t="n">
-        <v>98505</v>
+        <v>98508</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>82313249</v>
       </c>
       <c r="B8" t="n">
-        <v>98608</v>
+        <v>98611</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 29705-2021 artfynd.xlsx
+++ b/artfynd/A 29705-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>82313222</v>
       </c>
       <c r="B2" t="n">
-        <v>105627</v>
+        <v>105636</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>82313250</v>
       </c>
       <c r="B3" t="n">
-        <v>98609</v>
+        <v>98612</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>82313242</v>
       </c>
       <c r="B4" t="n">
-        <v>100309</v>
+        <v>100315</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>82313253</v>
       </c>
       <c r="B6" t="n">
-        <v>98492</v>
+        <v>98495</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>82313251</v>
       </c>
       <c r="B7" t="n">
-        <v>98508</v>
+        <v>98511</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>82313249</v>
       </c>
       <c r="B8" t="n">
-        <v>98611</v>
+        <v>98614</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 29705-2021 artfynd.xlsx
+++ b/artfynd/A 29705-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>82313222</v>
       </c>
       <c r="B2" t="n">
-        <v>105636</v>
+        <v>105639</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>82313250</v>
       </c>
       <c r="B3" t="n">
-        <v>98612</v>
+        <v>98613</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>82313242</v>
       </c>
       <c r="B4" t="n">
-        <v>100315</v>
+        <v>100316</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>82313263</v>
       </c>
       <c r="B5" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>82313253</v>
       </c>
       <c r="B6" t="n">
-        <v>98495</v>
+        <v>98496</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>82313251</v>
       </c>
       <c r="B7" t="n">
-        <v>98511</v>
+        <v>98512</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>82313249</v>
       </c>
       <c r="B8" t="n">
-        <v>98614</v>
+        <v>98615</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 29705-2021 artfynd.xlsx
+++ b/artfynd/A 29705-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>82313222</v>
       </c>
       <c r="B2" t="n">
-        <v>105639</v>
+        <v>105667</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>82313250</v>
       </c>
       <c r="B3" t="n">
-        <v>98613</v>
+        <v>98640</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>82313242</v>
       </c>
       <c r="B4" t="n">
-        <v>100316</v>
+        <v>100343</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>82313263</v>
       </c>
       <c r="B5" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>82313253</v>
       </c>
       <c r="B6" t="n">
-        <v>98496</v>
+        <v>98523</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>82313251</v>
       </c>
       <c r="B7" t="n">
-        <v>98512</v>
+        <v>98539</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>82313249</v>
       </c>
       <c r="B8" t="n">
-        <v>98615</v>
+        <v>98642</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 29705-2021 artfynd.xlsx
+++ b/artfynd/A 29705-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>82313222</v>
       </c>
       <c r="B2" t="n">
-        <v>105667</v>
+        <v>105673</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>82313250</v>
       </c>
       <c r="B3" t="n">
-        <v>98640</v>
+        <v>98646</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>82313242</v>
       </c>
       <c r="B4" t="n">
-        <v>100343</v>
+        <v>100349</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>82313263</v>
       </c>
       <c r="B5" t="n">
-        <v>97490</v>
+        <v>97496</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>82313253</v>
       </c>
       <c r="B6" t="n">
-        <v>98523</v>
+        <v>98529</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>82313251</v>
       </c>
       <c r="B7" t="n">
-        <v>98539</v>
+        <v>98545</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>82313249</v>
       </c>
       <c r="B8" t="n">
-        <v>98642</v>
+        <v>98648</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 29705-2021 artfynd.xlsx
+++ b/artfynd/A 29705-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>82313222</v>
       </c>
       <c r="B2" t="n">
-        <v>105673</v>
+        <v>105680</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>82313250</v>
       </c>
       <c r="B3" t="n">
-        <v>98646</v>
+        <v>98653</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>82313242</v>
       </c>
       <c r="B4" t="n">
-        <v>100349</v>
+        <v>100356</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>82313263</v>
       </c>
       <c r="B5" t="n">
-        <v>97496</v>
+        <v>97503</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>82313253</v>
       </c>
       <c r="B6" t="n">
-        <v>98529</v>
+        <v>98536</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>82313251</v>
       </c>
       <c r="B7" t="n">
-        <v>98545</v>
+        <v>98552</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>82313249</v>
       </c>
       <c r="B8" t="n">
-        <v>98648</v>
+        <v>98655</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 29705-2021 artfynd.xlsx
+++ b/artfynd/A 29705-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>82313222</v>
       </c>
       <c r="B2" t="n">
-        <v>105680</v>
+        <v>105684</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>82313250</v>
       </c>
       <c r="B3" t="n">
-        <v>98653</v>
+        <v>98657</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>82313242</v>
       </c>
       <c r="B4" t="n">
-        <v>100356</v>
+        <v>100360</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>82313263</v>
       </c>
       <c r="B5" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>82313253</v>
       </c>
       <c r="B6" t="n">
-        <v>98536</v>
+        <v>98540</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>82313251</v>
       </c>
       <c r="B7" t="n">
-        <v>98552</v>
+        <v>98556</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>82313249</v>
       </c>
       <c r="B8" t="n">
-        <v>98655</v>
+        <v>98659</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 29705-2021 artfynd.xlsx
+++ b/artfynd/A 29705-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>82313222</v>
       </c>
       <c r="B2" t="n">
-        <v>105684</v>
+        <v>105691</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>82313250</v>
       </c>
       <c r="B3" t="n">
-        <v>98657</v>
+        <v>98664</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>82313242</v>
       </c>
       <c r="B4" t="n">
-        <v>100360</v>
+        <v>100367</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>82313263</v>
       </c>
       <c r="B5" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>82313253</v>
       </c>
       <c r="B6" t="n">
-        <v>98540</v>
+        <v>98547</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>82313251</v>
       </c>
       <c r="B7" t="n">
-        <v>98556</v>
+        <v>98563</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>82313249</v>
       </c>
       <c r="B8" t="n">
-        <v>98659</v>
+        <v>98666</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 29705-2021 artfynd.xlsx
+++ b/artfynd/A 29705-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>82313222</v>
       </c>
       <c r="B2" t="n">
-        <v>105694</v>
+        <v>105699</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>82313250</v>
       </c>
       <c r="B3" t="n">
-        <v>98667</v>
+        <v>98672</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>82313242</v>
       </c>
       <c r="B4" t="n">
-        <v>100370</v>
+        <v>100375</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>82313263</v>
       </c>
       <c r="B5" t="n">
-        <v>97517</v>
+        <v>97522</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>82313253</v>
       </c>
       <c r="B6" t="n">
-        <v>98550</v>
+        <v>98555</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>82313251</v>
       </c>
       <c r="B7" t="n">
-        <v>98566</v>
+        <v>98571</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>82313249</v>
       </c>
       <c r="B8" t="n">
-        <v>98669</v>
+        <v>98674</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 29705-2021 artfynd.xlsx
+++ b/artfynd/A 29705-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>82313222</v>
       </c>
       <c r="B2" t="n">
-        <v>105699</v>
+        <v>105707</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>82313250</v>
       </c>
       <c r="B3" t="n">
-        <v>98672</v>
+        <v>98680</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>82313242</v>
       </c>
       <c r="B4" t="n">
-        <v>100375</v>
+        <v>100383</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>82313263</v>
       </c>
       <c r="B5" t="n">
-        <v>97522</v>
+        <v>97530</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>82313253</v>
       </c>
       <c r="B6" t="n">
-        <v>98555</v>
+        <v>98563</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>82313251</v>
       </c>
       <c r="B7" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>82313249</v>
       </c>
       <c r="B8" t="n">
-        <v>98674</v>
+        <v>98682</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
